--- a/output/2026-10-04_Malesia_Sarawak_ATEX_Equipment_Services.xlsx
+++ b/output/2026-10-04_Malesia_Sarawak_ATEX_Equipment_Services.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Distributore/rappresentante e stockist di apparecchiature elettriche per aree pericolose (illuminazione explosion-proof, stazioni di comando remoto, ventilatori, morsetti di messa a terra) certificate IECEx, ATEX, UL, CSA, FM. Verificato tramite sito ufficiale (WebFetch). Unica sede a Shah Alam; nessuna filiale in Sarawak riscontrata, copertura verso Sarawak da confermare direttamente con l'azienda.</t>
+          <t>Distributore/rappresentante e stockist di apparecchiature elettriche per aree pericolose (illuminazione explosion-proof, stazioni di comando remoto, ventilatori, morsetti di messa a terra) certificate IECEx, ATEX, UL, CSA, FM. Verificato tramite sito ufficiale (WebFetch). Unica sede a Shah Alam; nessuna filiale in Sarawak riscontrata, copertura verso Sarawak da confermare direttamente con l'azienda. [DUPLICATO — vedi anche: 2026-10-01_03_Malesia_Kedah_ATEX_Equipment_Services.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -533,7 +533,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gruppo regionale PPE/safety equipment quotato su Bursa Malaysia (LEAP Market), con filiale confermata a Kuching. Distribuisce anche strumentazione di monitoraggio e attrezzature per ambienti pericolosi/oil&amp;gas. Verificato tramite sito ufficiale e company profile del gruppo.</t>
+          <t>Gruppo regionale PPE/safety equipment quotato su Bursa Malaysia (LEAP Market), con filiale confermata a Kuching. Distribuisce anche strumentazione di monitoraggio e attrezzature per ambienti pericolosi/oil&amp;gas. Verificato tramite sito ufficiale e company profile del gruppo. [DUPLICATO — vedi anche: 2026-10-03_01_Malesia_Pahang_ATEX_Equipment_Services.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -548,7 +548,6 @@
           <t>Petro-Excel Sdn Bhd</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Lutong, Miri, Sarawak</t>
@@ -564,7 +563,6 @@
           <t>+6085-652333 (fax +6085-651222)</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Azienda Petronas-licensed (fondata 1999) specializzata nella fornitura e assistenza di apparecchiature per aree pericolose: gas detector, cable glands, beacon/sounders, light fittings, sistemi PAGA (Public Address and General Alarm). Sede confermata a Lutong, Miri, Sarawak. Nessun sito web/email reperiti; verificato tramite directory MATRADE/esportatori oil&amp;gas e altre fonti pubbliche.</t>
@@ -572,7 +570,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
